--- a/output/pdf_financials_xlsx/PRL.xlsx
+++ b/output/pdf_financials_xlsx/PRL.xlsx
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.161441</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.111704</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.158215</v>
       </c>
     </row>
     <row r="29">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.86396</v>
+        <v>7.025401</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6.122399</v>
+        <v>6.234103</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>14.747967</v>
+        <v>14.906182</v>
       </c>
     </row>
     <row r="30">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>9.34358369278684</v>
+        <v>9.563345680756933</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4.722283462299756</v>
+        <v>4.808442164447841</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6.501179538250707</v>
+        <v>6.570923667773394</v>
       </c>
     </row>
     <row r="31">
@@ -3605,15 +3605,19 @@
           <t>Depreciation of property and equipment 11</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
-        <v>-0.161441</v>
+        <v>0.161441</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.111704</v>
+        <v>0.111704</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.158215</v>
+        <v>0.158215</v>
       </c>
     </row>
     <row r="15">

--- a/output/pdf_financials_xlsx/PRL.xlsx
+++ b/output/pdf_financials_xlsx/PRL.xlsx
@@ -963,20 +963,14 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>5.245917</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>7.238761</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>7.658837</v>
       </c>
     </row>
     <row r="35">
@@ -985,20 +979,14 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1007,20 +995,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>5.245917</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>7.238761</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>7.658837</v>
       </c>
     </row>
     <row r="37">
@@ -1029,20 +1011,14 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1051,20 +1027,14 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1073,20 +1043,14 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1095,20 +1059,14 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>1.791145</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>4.371616</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>6.752364</v>
       </c>
     </row>
     <row r="41">
@@ -1117,20 +1075,14 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>1.791145</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>4.371616</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>6.752364</v>
       </c>
     </row>
     <row r="42">
@@ -1139,20 +1091,14 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1161,20 +1107,14 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1183,20 +1123,14 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1205,20 +1139,14 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1227,20 +1155,14 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1249,20 +1171,14 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1271,20 +1187,14 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1315,20 +1225,14 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1337,20 +1241,14 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1359,20 +1257,14 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1381,20 +1273,14 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1403,20 +1289,14 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1447,20 +1327,14 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1469,20 +1343,14 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1491,20 +1359,14 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>3.488176</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>2.978837</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2.641182</v>
       </c>
     </row>
     <row r="59">
@@ -1513,20 +1375,14 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>6.874877</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>7.912535</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>11.472976</v>
       </c>
     </row>
     <row r="60">
@@ -1535,20 +1391,14 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1557,20 +1407,14 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1601,20 +1445,14 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>79.05283300000001</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>149.498765</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>256.680546</v>
       </c>
     </row>
     <row r="64">
@@ -1623,20 +1461,14 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>2.737421</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>2.725548</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>2.296453</v>
       </c>
     </row>
     <row r="65">
@@ -1645,20 +1477,14 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1667,20 +1493,14 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1689,20 +1509,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>8.752679000000001</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>16.971189</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>16.161225</v>
       </c>
     </row>
     <row r="68">
@@ -1711,20 +1525,14 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>11.4901</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>19.696737</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>18.457678</v>
       </c>
     </row>
     <row r="69">
@@ -1733,20 +1541,14 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1755,20 +1557,14 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1777,20 +1573,14 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1799,20 +1589,14 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1821,20 +1605,14 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1843,20 +1621,14 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1865,20 +1637,14 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1909,20 +1675,14 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1931,20 +1691,14 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1953,20 +1707,14 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1997,20 +1745,14 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2019,20 +1761,14 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2041,20 +1777,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>1.179687</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0.07604</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>1.043901</v>
       </c>
     </row>
     <row r="84">
@@ -2063,20 +1793,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>1.179687</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0.07604</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1.043901</v>
       </c>
     </row>
     <row r="85">
@@ -2085,20 +1809,14 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2129,20 +1847,14 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>70.63736900000001</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>74.169523</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>175.039871</v>
       </c>
     </row>
     <row r="88">
@@ -2151,20 +1863,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>4.881037</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>78.95106199999999</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>78.952871</v>
       </c>
     </row>
     <row r="89">
@@ -2173,20 +1879,14 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2195,20 +1895,14 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>3.469653</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>-4.041467</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>1.030977</v>
       </c>
     </row>
     <row r="91">
@@ -2217,20 +1911,14 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2239,20 +1927,14 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0.064774</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0.419647</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>1.656827</v>
       </c>
     </row>
     <row r="93">
@@ -2261,20 +1943,14 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2283,20 +1959,14 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>8.415464</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>75.32924199999999</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>81.640675</v>
       </c>
     </row>
     <row r="95">
@@ -2305,20 +1975,14 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2327,20 +1991,14 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>8.415464</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>75.32924199999999</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>81.640675</v>
       </c>
     </row>
     <row r="97">
@@ -2349,20 +2007,14 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.1064536675111947</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.5038786909042359</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.3180633525689945</v>
       </c>
     </row>
     <row r="98">
@@ -2378,20 +2030,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>7.332388</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>6.562442</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>15.127447</v>
       </c>
     </row>
     <row r="100">
@@ -2400,20 +2046,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0.161441</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0.111704</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0.158215</v>
       </c>
     </row>
     <row r="101">
@@ -2422,20 +2062,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.862504</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>-2.580471</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>-2.380748</v>
       </c>
     </row>
     <row r="102">
@@ -2444,20 +2078,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2466,20 +2094,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.054407</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-1.035613</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.214617</v>
       </c>
     </row>
     <row r="104">
@@ -2488,20 +2110,14 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.225594</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>8.675426</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>-1.048633</v>
       </c>
     </row>
     <row r="105">
@@ -2510,20 +2126,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2532,20 +2142,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.582503</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>5.059342</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-3.643998</v>
       </c>
     </row>
     <row r="107">
@@ -2554,20 +2158,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.023879</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0.354873</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>1.237919</v>
       </c>
     </row>
     <row r="108">
@@ -2576,20 +2174,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2598,20 +2190,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2620,20 +2206,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2642,20 +2222,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>-0.115438</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>-0.103844</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>-0.18299</v>
       </c>
     </row>
     <row r="112">
@@ -2664,20 +2238,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2686,20 +2254,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2708,20 +2270,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2730,20 +2286,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2752,20 +2302,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2774,20 +2318,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2796,20 +2334,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2818,20 +2350,14 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-2.128753</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>-2.764364</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>-5.273648</v>
       </c>
     </row>
     <row r="120">
@@ -2840,20 +2366,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2862,20 +2382,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2884,20 +2398,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2906,20 +2414,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2928,20 +2430,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2950,20 +2446,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2972,20 +2462,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>-2.665681</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>-8.073562000000001</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>-10.055003</v>
       </c>
     </row>
     <row r="127">
@@ -3016,20 +2500,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3038,20 +2516,14 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>16.594285</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>56.590148</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>91.01447400000001</v>
       </c>
     </row>
     <row r="130">
@@ -3060,20 +2532,14 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>6.202895</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>5.245917</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>7.238761</v>
       </c>
     </row>
     <row r="131">
@@ -3082,20 +2548,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3104,20 +2564,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.956978</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>1.992844</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.420076</v>
       </c>
     </row>
     <row r="133">
@@ -3126,20 +2580,14 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>5.245917</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>7.238761</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>7.658837</v>
       </c>
     </row>
     <row r="134">
@@ -3148,20 +2596,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>-0.115438</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>-0.103844</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>-0.18299</v>
       </c>
     </row>
     <row r="135">
@@ -3170,20 +2612,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-15.537948</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-51.936784</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-85.50373999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3197,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3246,942 +2682,3240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Revenue 7</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>73.461749</v>
+        <v>5.245917</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>129.649121</v>
+        <v>7.238761</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>226.850634</v>
+        <v>7.658837</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Provision for loan losses and other liabilities 6</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Restricted cash 5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n">
-        <v>24.756892</v>
+        <v>7.875106</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>55.021098</v>
+        <v>16.286887</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>120.152745</v>
+        <v>22.615319</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Acquisition and data</t>
+          <t>Loans and advances receivable 6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="5" t="n">
-        <v>12.903185</v>
+        <v>49.777458</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>23.697576</v>
+        <v>103.849824</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>27.230127</v>
+        <v>195.628431</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salaries, wages and benefits 17, 21</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Other receivables 9</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
-        <v>12.53474</v>
+        <v>1.791145</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>21.376719</v>
+        <v>4.371616</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>26.709694</v>
+        <v>6.752364</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Prepaids 8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.625771</v>
+        <v>0.450959</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4.649162</v>
+        <v>1.486572</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8.844587000000001</v>
+        <v>1.701189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Processing and technology</t>
+          <t>Derivative financial instruments 10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="5" t="n">
-        <v>3.379515</v>
+        <v>0.352937</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>5.797</v>
+        <v>0.040173</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>10.029943</v>
+        <v>0.021693</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Property and equipment 11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>31.443211</v>
+        <v>0.507718</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>55.520457</v>
+        <v>0.499858</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>72.814351</v>
+        <v>0.524633</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Operating income</t>
+          <t>Deferred tax assets 18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>DeferredTaxAssets</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>17.261646</v>
+        <v>3.196258</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>19.107566</v>
+        <v>5.33356</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>33.883538</v>
+        <v>8.210248</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Interest and fees on credit facilities 15</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Right-of-use assets 13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
-        <v>-2.316836</v>
+        <v>2.980458</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-4.431071</v>
+        <v>2.478979</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-9.784859000000001</v>
+        <v>2.116549</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Interest on term loan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Intangible assets 12</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
-        <v>-1.735947</v>
+        <v>6.874877</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.886852</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.912535</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>11.472976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Interest expense on lease liabilities 13</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>InterestExpenseNonOperating</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.468428</v>
+        <v>79.05283300000001</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.440043</v>
+        <v>149.498765</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.37948</v>
+        <v>256.680546</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amortization of internally developed software 12</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Accounts payable 14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AccountsPayable</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
-        <v>-1.573296</v>
+        <v>2.737421</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-2.140366</v>
+        <v>2.725548</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-2.596779</v>
+        <v>2.296453</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Depreciation of property and equipment 11</t>
+          <t>Accrued liabilities 14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
+          <t>CurrentAccruedExpenses</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.161441</v>
+        <v>8.752679000000001</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.111704</v>
+        <v>16.971189</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.158215</v>
+        <v>16.161225</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amortization of right-of-use assets 13</t>
+          <t>Credit facilities 15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="5" t="n">
-        <v>-0.716939</v>
+        <v>38.1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.660778</v>
+        <v>46.87</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.6218900000000001</v>
+        <v>148.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Income taxes payable</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.135619</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.451466</v>
+        <v>4.343009</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.058093</v>
+        <v>3.944569</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Unrealized loss on derivative financial</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unrealized loss on derivative financial</t>
+          <t>Lease liabilities 13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="5" t="n">
+        <v>3.53626</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-0.312764</v>
+        <v>3.183737</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.061866</v>
+        <v>2.67203</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>instruments</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Total other expenses</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred tax liabilities 18</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.179687</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-9.435044</v>
+        <v>0.07604</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-13.661182</v>
+        <v>1.043901</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Income before transaction costs and income</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Income before transaction costs and income total</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>70.63736900000001</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>9.672522000000001</v>
+        <v>74.169523</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>20.222356</v>
+        <v>175.039871</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Transaction costs</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital 16</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>4.881037</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1.60825</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>78.95106199999999</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>78.952871</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Current 18</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Retained earnings (deficit)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>3.469653</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>4.74278</v>
+        <v>-4.041467</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>7.003736</v>
+        <v>1.030977</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Deferred 18</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Contributed surplus 17</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.064774</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-3.24095</v>
+        <v>0.419647</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-1.908827</v>
+        <v>1.656827</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Net income for the year</t>
+          <t>Total Shareholders' Equity</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>7.332388</v>
+        <v>8.415464</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>6.562442</v>
+        <v>75.32924199999999</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>15.127447</v>
+        <v>81.640675</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Total Liabilities and Shareholders' Equity</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
-        <v>23.561005</v>
+        <v>79.05283300000001</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>27.459552</v>
+        <v>149.498765</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>34.325137</v>
+        <v>256.680546</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>outstanding</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t>Term loans 15</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>24.221218</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>28.108642</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>35.704078</v>
+        <v>11.195703</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Cash flows from (used in) operating activities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Basic $</t>
+          <t>Net income</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3.1e-07</v>
+        <v>7.332388</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2.4e-07</v>
+        <v>6.562442</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>4.4e-07</v>
+        <v>15.127447</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Diluted $</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Provision for loan losses 6</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>3e-07</v>
+        <v>24.246077</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2.3e-07</v>
+        <v>50.284082</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>4.2e-07</v>
+        <v>119.449722</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>-0.147433</v>
+          <t>Unrealized loss on derivative financial instruments 10</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.451466</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.312764</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.061866</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Total other income (expenses)</t>
+          <t>Deferred income tax recovery 18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>-6.839867</v>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-9.435044</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.240949</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.908827</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Amortization of acquisition transaction costs and</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Income before transaction costs and income tax</t>
+          <t>Amortization of acquisition transaction costs and</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>10.421779</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>9.672522000000001</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.094144</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>8.641636999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>customer acquisition data</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Transaction costs</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Depreciation of property and equipment 11</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.60825</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.111704</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.158215</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>customer acquisition data</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Amortization of internally developed software 12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>3.871102</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>4.74278</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.140366</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2.596779</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>customer acquisition data</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Amortization of right-of-use assets 13</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.660778</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.6218900000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>customer acquisition data</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 17</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.354873</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1.237919</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>customer acquisition data</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>customer acquisition data total</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>62.280204</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>145.986648</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Restricted cash 5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" s="5" t="n">
+        <v>-2.293852</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>-8.411781</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-6.328432</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Prepaids 8</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.054407</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>-1.035613</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.214617</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Acquisition transaction costs and customer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Acquisition transaction costs and customer</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-7.245524</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-9.788195999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>acquisition data</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Other receivables 9</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-2.580471</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-2.380748</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>acquisition data</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Income taxes recoverable/payable 18</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>-0.79261</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-0.39844</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>acquisition data</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Accounts payable and accrued liabilities 14</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>8.675426</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>-1.048633</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>acquisition data</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Net additions of loans and advances receivable 6</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>-109.631634</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-227.823735</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>acquisition data</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Principal loans and advances receivable recoveries 6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>6.909063</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>16.675403</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>acquisition data</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>-51.83294</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-85.32075</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Advances from credit facilities 15</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>37.12</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>113.155</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Payments on credit facilities 15</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" s="5" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>-28.35</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-11.125</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Repayments from term loans</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>-11.195703</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Payments on lease liabilities 13</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" s="5" t="n">
+        <v>-0.9874579999999999</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>-0.980612</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.961593</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-2.665681</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>-8.073562000000001</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-10.055003</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Proceeds from shares issued 16</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>67.67139299999999</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Proceeds from options exercised 16</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.398632</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.00107</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>56.590148</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>91.01447400000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Purchases of property and equipment 11</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>-0.115438</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-0.103844</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.18299</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cost of internally developed software 12</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>-2.013315</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-2.66052</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-5.090658</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>-2.764364</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-5.273648</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-0.956978</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>1.992844</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.420076</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>6.202895</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>5.245917</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>7.238761</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Cash, end of period</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>5.245917</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>7.238761</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>7.658837</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Interest received</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>20.408476</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>19.140259</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>16.535277</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>3.536539</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>5.374717</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>8.543037999999999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Income taxes paid</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>5.645848</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>7.473222</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Non-cash dividend</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Deferred income tax expense (recovery) 18</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>-0.781711</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-3.240949</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Depreciation of property and equipment 11</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.161441</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.111704</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Amortization of internally developed software 12</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>1.573296</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>2.140366</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Amortization of right-of-use assets 13</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>0.716939</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.660778</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 17</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.023879</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.354873</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Items not affecting cash total</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>35.00906</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>62.280204</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Other receivables 9</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>-0.862504</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-2.580471</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Income taxes recoverable/payable 18</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>3.853968</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>-0.79261</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Accounts payable and accrued liabilities 14</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.225594</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>8.675426</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Net additions of loans and advances receivable 6</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>-51.269799</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-109.631634</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Principal loans and advances receivable recoveries 6</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>3.874018</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>6.909063</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Net cash from (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>-15.42251</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>-51.83294</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Advances (repayments) from term loans</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>1.838615</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>-11.195703</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Proceeds from options exercised 17</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>0.108809</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.398632</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Net cash from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>16.594285</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>56.590148</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Net cash from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-2.128753</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-2.764364</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Non-cash dividend 21</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Revenue 7</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>73.461749</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>129.649121</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>226.850634</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Provision for loan losses and other liabilities 6</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" s="5" t="n">
+        <v>24.756892</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>55.021098</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>120.152745</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Acquisition and data</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>12.903185</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>23.697576</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>27.230127</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Salaries, wages and benefits 17, 21</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>12.53474</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>21.376719</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>26.709694</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>2.625771</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>4.649162</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>8.844587000000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Processing and technology</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>3.379515</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>5.797</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>10.029943</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>31.443211</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>55.520457</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>72.814351</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>17.261646</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>19.107566</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>33.883538</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Interest and fees on credit facilities 15</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>-2.316836</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-4.431071</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-9.784859000000001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Interest on term loan</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>-1.735947</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-0.886852</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Interest expense on lease liabilities 13</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>-0.468428</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-0.440043</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-0.37948</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Amortization of internally developed software 12</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" s="5" t="n">
+        <v>-1.573296</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>-2.140366</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-2.596779</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Depreciation of property and equipment 11</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0.161441</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.111704</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.158215</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Amortization of right-of-use assets 13</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>-0.716939</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-0.660778</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-0.6218900000000001</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-0.451466</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.058093</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Unrealized loss on derivative financial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Unrealized loss on derivative financial</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.312764</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.061866</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>instruments</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Total other expenses</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>-9.435044</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>-13.661182</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Income before transaction costs and income</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Income before transaction costs and income total</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>9.672522000000001</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>20.222356</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Transaction costs</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>1.60825</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>Income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Current 18</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>4.74278</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>7.003736</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Deferred 18</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>-3.24095</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>-1.908827</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Net income for the year</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>7.332388</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>6.562442</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>15.127447</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>23.561005</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>27.459552</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>34.325137</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>24.221218</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>28.108642</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>35.704078</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Basic $</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>3.1e-07</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>2.4e-07</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>4.4e-07</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Diluted $</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>3e-07</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>2.3e-07</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>4.2e-07</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>-0.147433</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>-0.451466</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Total other income (expenses)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>-6.839867</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>-9.435044</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Income before transaction costs and income tax</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="n">
+        <v>10.421779</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>9.672522000000001</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Transaction costs</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>1.60825</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
+        <v>3.871102</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>4.74278</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
         <v>-0.781711</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F111" s="5" t="n">
         <v>-3.24095</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
